--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3589" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="353">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,10 +559,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -5360,7 +5363,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>176</v>
       </c>
@@ -5373,13 +5376,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5390,8 +5393,12 @@
       <c r="K39" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
+      <c r="L39" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5461,10 +5468,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5478,7 +5485,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5487,13 +5494,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5544,7 +5551,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5564,10 +5571,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5663,12 +5670,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5678,13 +5685,13 @@
         <v>62</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5697,7 +5704,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5709,7 +5716,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5748,7 +5755,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5766,28 +5773,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5800,7 +5807,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5812,7 +5819,7 @@
         <v>74</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>74</v>
@@ -5851,7 +5858,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5871,17 +5878,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5903,7 +5910,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5915,7 +5922,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -5954,7 +5961,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5974,17 +5981,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6006,7 +6013,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6057,7 +6064,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6075,28 +6082,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6109,7 +6116,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6121,7 +6128,7 @@
         <v>74</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>74</v>
@@ -6160,7 +6167,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6180,10 +6187,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6206,11 +6213,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6261,7 +6268,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6281,10 +6288,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6311,7 +6318,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6362,7 +6369,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6382,17 +6389,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6410,11 +6417,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6465,7 +6472,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6485,17 +6492,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6513,11 +6520,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6568,7 +6575,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6588,17 +6595,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6616,11 +6623,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6671,7 +6678,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6691,10 +6698,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6708,7 +6715,7 @@
         <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6717,13 +6724,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6774,7 +6781,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6794,10 +6801,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6811,7 +6818,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6820,13 +6827,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6877,7 +6884,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6897,10 +6904,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6923,7 +6930,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6976,7 +6983,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6996,10 +7003,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7055,25 +7062,25 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7093,10 +7100,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7119,7 +7126,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7172,7 +7179,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7192,10 +7199,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7218,7 +7225,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7271,7 +7278,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7291,10 +7298,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7317,7 +7324,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7370,7 +7377,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7390,10 +7397,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7407,7 +7414,7 @@
         <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7416,7 +7423,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7457,7 +7464,7 @@
         <v>74</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -7467,7 +7474,7 @@
         <v>124</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7487,13 +7494,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>74</v>
@@ -7515,7 +7522,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7568,7 +7575,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7588,10 +7595,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7689,10 +7696,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7790,10 +7797,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7891,10 +7898,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7992,10 +7999,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8095,10 +8102,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8198,10 +8205,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8301,10 +8308,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8404,10 +8411,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8505,10 +8512,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8538,7 +8545,7 @@
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
@@ -8564,7 +8571,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8582,7 +8589,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8602,10 +8609,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8639,7 +8646,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>74</v>
@@ -8681,7 +8688,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8701,10 +8708,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8727,7 +8734,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8780,7 +8787,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8800,10 +8807,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8826,7 +8833,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8879,7 +8886,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8899,10 +8906,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8925,7 +8932,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8978,7 +8985,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8998,10 +9005,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9024,7 +9031,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9077,7 +9084,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9097,10 +9104,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9123,7 +9130,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9176,7 +9183,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9196,10 +9203,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9222,10 +9229,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9277,7 +9284,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9297,10 +9304,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9323,7 +9330,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9376,7 +9383,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9396,10 +9403,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9422,7 +9429,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9475,7 +9482,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9495,10 +9502,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9521,7 +9528,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9574,7 +9581,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9594,13 +9601,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>74</v>
@@ -9622,7 +9629,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9675,7 +9682,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9695,10 +9702,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9796,10 +9803,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9897,10 +9904,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9998,10 +10005,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10099,10 +10106,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10202,10 +10209,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10305,10 +10312,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10408,10 +10415,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10511,10 +10518,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10612,10 +10619,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10645,7 +10652,7 @@
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
@@ -10671,7 +10678,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -10689,7 +10696,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10709,10 +10716,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10746,7 +10753,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>74</v>
@@ -10788,7 +10795,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10808,10 +10815,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10834,10 +10841,10 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -10889,7 +10896,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10909,10 +10916,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10935,7 +10942,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10988,7 +10995,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11008,10 +11015,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11034,7 +11041,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11087,7 +11094,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11107,10 +11114,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11133,7 +11140,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11186,7 +11193,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11206,10 +11213,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11232,7 +11239,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11285,7 +11292,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11305,10 +11312,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11331,7 +11338,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11384,7 +11391,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11404,10 +11411,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11430,7 +11437,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11483,7 +11490,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11503,10 +11510,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11529,7 +11536,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11582,7 +11589,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11602,10 +11609,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11628,7 +11635,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11681,7 +11688,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11701,10 +11708,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11727,7 +11734,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11780,7 +11787,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11800,10 +11807,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11901,10 +11908,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12002,10 +12009,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12103,10 +12110,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12204,10 +12211,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12307,10 +12314,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12410,10 +12417,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12513,10 +12520,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12616,10 +12623,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12717,10 +12724,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12747,7 +12754,7 @@
       </c>
       <c r="L112" s="2"/>
       <c r="M112" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -12756,7 +12763,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>74</v>
@@ -12798,7 +12805,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12818,10 +12825,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12855,7 +12862,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>74</v>
@@ -12897,7 +12904,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -12917,10 +12924,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12943,7 +12950,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -12996,7 +13003,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
